--- a/wanlong_retail_orders_fy_2025-05-01_2026-04-30.xlsx
+++ b/wanlong_retail_orders_fy_2025-05-01_2026-04-30.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC187"/>
+  <dimension ref="A1:BD187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -767,6 +767,11 @@
           <t>正/闭</t>
         </is>
       </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>七色米订单号</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -893,6 +898,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1019,6 +1025,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1145,6 +1152,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1271,6 +1279,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1397,6 +1406,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1523,6 +1533,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1649,6 +1660,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1775,6 +1787,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1936,6 +1949,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2112,6 +2126,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2258,6 +2273,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2399,6 +2415,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2545,6 +2562,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2691,6 +2709,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2867,6 +2886,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3043,6 +3063,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3189,6 +3210,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3335,6 +3357,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3511,6 +3534,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3657,6 +3681,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3803,6 +3828,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3979,6 +4005,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4125,6 +4152,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4301,6 +4329,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4477,6 +4506,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4641,6 +4671,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>XSD20251025000A</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4805,6 +4840,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>XSD20251025001A</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4979,6 +5019,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>XSD20251025002A</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5153,6 +5198,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>XSD20251025003A</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5358,6 +5408,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5532,6 +5583,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>XSD20251118003A</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5706,6 +5762,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>XSD20251028001A</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5880,6 +5941,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>XSD20251028002A</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6052,6 +6118,11 @@
       <c r="BC35" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>XSD20251028000A</t>
         </is>
       </c>
     </row>
@@ -6203,6 +6274,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6352,6 +6424,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6526,6 +6599,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>XSD20251031000A</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6700,6 +6778,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>XSD20251101000A</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6874,6 +6957,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>XSD20251101001A</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7048,6 +7136,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>XSD20251101002A</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7222,6 +7315,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>XSD20251101003A</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -7396,6 +7494,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>XSD20251101004A</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7570,6 +7673,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>XSD20251102000A</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7744,6 +7852,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>XSD20251106000A</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7949,6 +8062,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -8123,6 +8237,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>XSD20251107000A</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -8297,6 +8416,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>XSD20251107001A</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -8471,6 +8595,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>XSD20251108000A</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -8676,6 +8805,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>XSD20251108001A</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -8850,6 +8984,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>XSD20251108002I</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -9014,6 +9153,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>XSD20251109000A</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -9186,6 +9330,11 @@
       <c r="BC53" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>XSD20251109001A</t>
         </is>
       </c>
     </row>
@@ -9337,6 +9486,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -9509,6 +9659,11 @@
       <c r="BC55" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>XSD20251109002A</t>
         </is>
       </c>
     </row>
@@ -9645,6 +9800,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -9794,6 +9950,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -9968,6 +10125,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>XSD20251113001A</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -10142,6 +10304,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>XSD20251111001A</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -10301,6 +10468,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>XSD20251112002A</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -10465,6 +10637,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>XSD20251112000I</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -10629,6 +10806,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>XSD20251112003A</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -10801,6 +10983,11 @@
       <c r="BC63" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>XSD20251113000A</t>
         </is>
       </c>
     </row>
@@ -10952,6 +11139,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -11101,6 +11289,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -11275,6 +11464,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>XSD20251116000A</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -11449,6 +11643,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>XSD20251118000A</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -11623,6 +11822,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>XSD20251119000A</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -11797,6 +12001,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>XSD20251120000A</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -11971,6 +12180,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>XSD20251122000A</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -12145,6 +12359,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>XSD20251122001A</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -12319,6 +12538,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>XSD20251124000A</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -12493,6 +12717,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>XSD20251124002A</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -12688,6 +12917,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>XSD20251124003A</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -12862,6 +13096,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>XSD20251124004A</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -13036,6 +13275,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>XSD20251125001A</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -13210,6 +13454,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>XSD20251125000A</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -13384,6 +13633,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>XSD20251128000A</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -13548,6 +13802,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>XSD20251126001A</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -13722,6 +13981,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>XSD20251126004A</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -13896,6 +14160,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>XSD20251127000A</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -14070,6 +14339,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>XSD20251206004A</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -14234,6 +14508,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>XSD20251127002I</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -14386,6 +14665,11 @@
       <c r="BC84" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>XSD20251129000A</t>
         </is>
       </c>
     </row>
@@ -14537,6 +14821,11 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>XSD20251201003A</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -14711,6 +15000,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>XSD20251201000A</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -14885,6 +15179,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -15059,6 +15354,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>XSD20251202004A</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -15233,6 +15533,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>XSD20251205000A</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -15397,6 +15702,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>XSD20251206000A</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -15561,6 +15871,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>XSD20251206003A</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -15735,6 +16050,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>XSD20251206008A</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -15909,6 +16229,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>XSD20251206011A</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -16083,6 +16408,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>XSD20251206012A</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -16255,6 +16585,11 @@
       <c r="BC95" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>XSD20251209003I</t>
         </is>
       </c>
     </row>
@@ -16401,6 +16736,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -16575,6 +16911,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>XSD20251209001A</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -16739,6 +17080,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>XSD20251211001A</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -16913,6 +17259,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>XSD20251218002A</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -17077,6 +17428,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>XSD20251214004A</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -17249,6 +17605,11 @@
       <c r="BC101" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>XSD20251218001A</t>
         </is>
       </c>
     </row>
@@ -17400,6 +17761,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>XSD20251215000A</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -17574,6 +17940,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>XSD20251215003A</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -17746,6 +18117,11 @@
       <c r="BC104" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>XSD20251215005A</t>
         </is>
       </c>
     </row>
@@ -17897,6 +18273,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -18071,6 +18448,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>XSD20251216002A</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -18245,6 +18627,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>XSD20251218000A</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -18409,6 +18796,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>XSD20251219003A</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -18581,6 +18973,11 @@
       <c r="BC109" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>XSD20251221002I</t>
         </is>
       </c>
     </row>
@@ -18732,6 +19129,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>XSD20251220007A</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -18906,6 +19308,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>XSD20251221001A</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -19080,6 +19487,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>XSD20251221013A</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -19254,6 +19666,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>XSD20251222005A</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -19428,6 +19845,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>XSD20251224008A</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -19602,6 +20024,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>XSD20251224007A</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -19776,6 +20203,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>XSD20251226004A</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -19950,6 +20382,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>XSD20251224000A</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -20124,6 +20561,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>XSD20251225005A</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -20298,6 +20740,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>XSD20251226003A</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -20472,6 +20919,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>XSD20251227002A</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -20644,6 +21096,11 @@
       <c r="BC121" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>XSD20251231008A</t>
         </is>
       </c>
     </row>
@@ -20795,6 +21252,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -20944,6 +21402,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -21093,6 +21552,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -21242,6 +21702,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -21391,6 +21852,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -21565,6 +22027,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD127" t="inlineStr">
+        <is>
+          <t>XSD20260106005A</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -21739,6 +22206,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD128" t="inlineStr">
+        <is>
+          <t>XSD20251231009A</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -21913,6 +22385,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD129" t="inlineStr">
+        <is>
+          <t>XSD20260101018A</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -22087,6 +22564,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD130" t="inlineStr">
+        <is>
+          <t>XSD20260105000A</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -22259,6 +22741,11 @@
       <c r="BC131" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD131" t="inlineStr">
+        <is>
+          <t>XSD20260109010A</t>
         </is>
       </c>
     </row>
@@ -22410,6 +22897,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -22559,6 +23047,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -22708,6 +23197,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD134" t="inlineStr">
+        <is>
+          <t>XSD20260110007A</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -22887,6 +23381,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -23061,6 +23556,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD136" t="inlineStr">
+        <is>
+          <t>XSD20260111006A</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -23233,6 +23733,11 @@
       <c r="BC137" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD137" t="inlineStr">
+        <is>
+          <t>XSD20260116003A</t>
         </is>
       </c>
     </row>
@@ -23384,6 +23889,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD138" t="inlineStr">
+        <is>
+          <t>XSD20260117011A</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -23546,6 +24056,11 @@
       <c r="BC139" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD139" t="inlineStr">
+        <is>
+          <t>XSD20260118005A</t>
         </is>
       </c>
     </row>
@@ -23697,6 +24212,7 @@
           <t>关闭</t>
         </is>
       </c>
+      <c r="BD140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -23871,6 +24387,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD141" t="inlineStr">
+        <is>
+          <t>XSD20260119008A</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -24035,6 +24556,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD142" t="inlineStr">
+        <is>
+          <t>XSD20260119009A</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -24207,6 +24733,11 @@
       <c r="BC143" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD143" t="inlineStr">
+        <is>
+          <t>XSD20260124000A</t>
         </is>
       </c>
     </row>
@@ -24358,6 +24889,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD144" t="inlineStr">
+        <is>
+          <t>XSD20260124013A</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -24507,6 +25043,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD145" t="inlineStr">
+        <is>
+          <t>XSD20260124012A</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -24671,6 +25212,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD146" t="inlineStr">
+        <is>
+          <t>XSD20260125002A</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -24843,6 +25389,11 @@
       <c r="BC147" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD147" t="inlineStr">
+        <is>
+          <t>XSD20260125009A</t>
         </is>
       </c>
     </row>
@@ -24994,6 +25545,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -25153,6 +25705,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD149" t="inlineStr">
+        <is>
+          <t>XSD20260125010A</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -25317,6 +25874,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD150" t="inlineStr">
+        <is>
+          <t>XSD20260128001A</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -25481,6 +26043,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD151" t="inlineStr">
+        <is>
+          <t>XSD20260128000A</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -25655,6 +26222,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD152" t="inlineStr">
+        <is>
+          <t>XSD20260131001A</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -25829,6 +26401,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD153" t="inlineStr">
+        <is>
+          <t>XSD20260131007A</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -26003,6 +26580,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD154" t="inlineStr">
+        <is>
+          <t>XSD20260201000A</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -26177,6 +26759,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD155" t="inlineStr">
+        <is>
+          <t>XSD20260204002A</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -26351,6 +26938,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD156" t="inlineStr">
+        <is>
+          <t>XSD20260207002A</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -26525,6 +27117,7 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -26699,6 +27292,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD158" t="inlineStr">
+        <is>
+          <t>XSD20260208002A</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -26873,6 +27471,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD159" t="inlineStr">
+        <is>
+          <t>XSD20260208000A</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -27037,6 +27640,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD160" t="inlineStr">
+        <is>
+          <t>XSD20260210006A</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -27211,6 +27819,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD161" t="inlineStr">
+        <is>
+          <t>XSD20260209007I</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -27385,6 +27998,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD162" t="inlineStr">
+        <is>
+          <t>XSD20260212006A</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -27559,6 +28177,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD163" t="inlineStr">
+        <is>
+          <t>XSD20260220002A</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -27733,6 +28356,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD164" t="inlineStr">
+        <is>
+          <t>XSD20260216000A</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -27907,6 +28535,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD165" t="inlineStr">
+        <is>
+          <t>XSD20260220001A</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -28081,6 +28714,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD166" t="inlineStr">
+        <is>
+          <t>XSD20260223000A</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -28255,6 +28893,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD167" t="inlineStr">
+        <is>
+          <t>XSD20260220005A</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -28429,6 +29072,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD168" t="inlineStr">
+        <is>
+          <t>XSD20260221001A</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -28603,6 +29251,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD169" t="inlineStr">
+        <is>
+          <t>XSD20260221002A</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -28777,6 +29430,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD170" t="inlineStr">
+        <is>
+          <t>XSD20260222003A</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -28951,6 +29609,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD171" t="inlineStr">
+        <is>
+          <t>XSD20260223001A</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -29120,6 +29783,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD172" t="inlineStr">
+        <is>
+          <t>XSD20260223004A</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -29284,6 +29952,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD173" t="inlineStr">
+        <is>
+          <t>XSD20260223005A</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -29456,6 +30129,11 @@
       <c r="BC174" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD174" t="inlineStr">
+        <is>
+          <t>XSD20260225006A</t>
         </is>
       </c>
     </row>
@@ -29607,6 +30285,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD175" t="inlineStr">
+        <is>
+          <t>XSD20260228000A</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -29781,6 +30464,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD176" t="inlineStr">
+        <is>
+          <t>XSD20260302001I</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -29955,6 +30643,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD177" t="inlineStr">
+        <is>
+          <t>XSD20260305000A</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -30129,6 +30822,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD178" t="inlineStr">
+        <is>
+          <t>XSD20260307004A</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -30303,6 +31001,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD179" t="inlineStr">
+        <is>
+          <t>XSD20260307003A</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -30467,6 +31170,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD180" t="inlineStr">
+        <is>
+          <t>XSD20260308000A</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -30641,6 +31349,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD181" t="inlineStr">
+        <is>
+          <t>XSD20260314000A</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -30815,6 +31528,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD182" t="inlineStr">
+        <is>
+          <t>XSD20260315001A</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -30989,6 +31707,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD183" t="inlineStr">
+        <is>
+          <t>XSD20260318000A</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -31153,6 +31876,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD184" t="inlineStr">
+        <is>
+          <t>XSD20260320000A</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -31327,6 +32055,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD185" t="inlineStr">
+        <is>
+          <t>XSD20260322001A</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -31501,6 +32234,11 @@
           <t>正常</t>
         </is>
       </c>
+      <c r="BD186" t="inlineStr">
+        <is>
+          <t>XSD20260324000A</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -31673,6 +32411,11 @@
       <c r="BC187" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+      <c r="BD187" t="inlineStr">
+        <is>
+          <t>XSD20260405000A</t>
         </is>
       </c>
     </row>
@@ -31836,7 +32579,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>2088002319285895</t>
@@ -32184,7 +32926,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>2088702560710495</t>
@@ -32224,7 +32965,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>2088422544604706</t>
@@ -33198,7 +33938,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>2088702816169840</t>
@@ -33326,8 +34065,6 @@
           <t>肖志强工作微信转账</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>2025-11-09</t>
@@ -33450,7 +34187,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>2088442103176165</t>
@@ -33490,8 +34226,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>2025-11-12</t>
@@ -33526,7 +34260,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>2088442103176165</t>
@@ -33962,7 +34695,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>2088002001837940</t>
@@ -34196,7 +34928,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>2088002458970722</t>
@@ -34368,8 +35099,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>2025-11-27</t>
@@ -34624,7 +35353,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>2088032973401162</t>
@@ -34664,7 +35392,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>2088432508420509</t>
@@ -34924,8 +35651,6 @@
           <t>现金</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>2025-12-11</t>
@@ -35004,7 +35729,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>2088002898257722</t>
@@ -35264,7 +35988,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>2088422889325847</t>
@@ -36184,7 +36907,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>2088052511011514</t>
@@ -36268,7 +36990,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>2088632382663917</t>
@@ -36352,8 +37073,6 @@
           <t>现金</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>2026-01-24</t>
@@ -36476,7 +37195,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>2088832517321329</t>
@@ -36516,7 +37234,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>2088832517321329</t>
@@ -36908,7 +37625,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
           <t>2088342071507333</t>
@@ -37476,7 +38192,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
           <t>2088542899211586</t>
@@ -37736,7 +38451,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>2088002898257722</t>
@@ -37908,8 +38622,6 @@
           <t>现金</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>2026-03-20</t>
@@ -38139,7 +38851,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>WT_LS_251011_00004_ZF_02</t>
@@ -38455,7 +39166,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>WT_LS_251025_00001_ZF_01</t>
@@ -38491,7 +39201,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>WT_LS_251025_00002_ZF_01</t>
@@ -39447,7 +40156,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>WT_LS_251109_00001_ZF_01</t>
@@ -39563,8 +40271,6 @@
           <t>肖志强工作微信转账</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>支付</t>
@@ -39715,7 +40421,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>WT_LS_251112_00001_ZF_01</t>
@@ -39751,8 +40456,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>支付</t>
@@ -39783,7 +40486,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>WT_LS_251112_00003_ZF_01</t>
@@ -40179,7 +40881,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>WT_LS_251124_00003_ZF_01</t>
@@ -40255,7 +40956,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>WT_LS_251124_00003_ZF_01_TK_01</t>
@@ -40411,7 +41111,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>WT_LS_251126_00001_ZF_01</t>
@@ -40567,8 +41266,6 @@
           <t>微信转账</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>支付</t>
@@ -40799,7 +41496,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>WT_LS_251206_00001_ZF_01</t>
@@ -40835,7 +41531,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>WT_LS_251206_00002_ZF_01</t>
@@ -41071,8 +41766,6 @@
           <t>现金</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>支付</t>
@@ -41143,7 +41836,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
           <t>WT_LS_251214_00001_ZF_01</t>
@@ -41379,7 +42071,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
           <t>WT_LS_251219_00001_ZF_01</t>
@@ -42215,7 +42906,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
           <t>WT_LS_260118_00001_ZF_01</t>
@@ -42291,7 +42981,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
           <t>WT_LS_260119_00003_ZF_01</t>
@@ -42367,8 +43056,6 @@
           <t>现金</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>支付</t>
@@ -42479,7 +43166,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
           <t>WT_LS_260128_00001_ZF_01</t>
@@ -42515,7 +43201,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
           <t>WT_LS_260128_00002_ZF_01</t>
@@ -42871,7 +43556,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
           <t>WT_LS_260208_00003_ZF_01</t>
@@ -43387,7 +44071,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>WT_LS_260223_00003_ZF_01</t>
@@ -43623,7 +44306,6 @@
           <t>支付宝</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
           <t>WT_LS_260308_00001_ZF_01</t>
@@ -43779,8 +44461,6 @@
           <t>现金</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr"/>
-      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
           <t>支付</t>
